--- a/kbl/root/小学G1-G6数学知识点.xlsx
+++ b/kbl/root/小学G1-G6数学知识点.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhanggaozhang/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhanggaozhang/Code/Homework Help/kbl/root/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA8F059-7EE8-8947-BA45-4877F1E7A805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269AC1CB-35BB-924E-B691-31405F1EE308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="340" yWindow="620" windowWidth="28100" windowHeight="16740" xr2:uid="{42060C19-F99B-5D4B-B87E-BC78766BC6C2}"/>
   </bookViews>
@@ -4168,7 +4168,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A69C5E3E-8CEE-9D4D-88A8-B62C489FB538}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H447"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -4210,7 +4209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="82" hidden="1" customHeight="1">
+    <row r="2" spans="1:8" ht="82" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4236,7 +4235,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="54" hidden="1" customHeight="1">
+    <row r="3" spans="1:8" ht="54" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -4262,7 +4261,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="46" hidden="1" customHeight="1">
+    <row r="4" spans="1:8" ht="46" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -4288,7 +4287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="36" hidden="1" customHeight="1">
+    <row r="5" spans="1:8" ht="36" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -4314,7 +4313,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="33" hidden="1" customHeight="1">
+    <row r="6" spans="1:8" ht="33" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -4340,7 +4339,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="7" spans="1:8" ht="26" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -4366,7 +4365,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="8" spans="1:8" ht="26" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -4392,7 +4391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="9" spans="1:8" ht="26" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -4418,7 +4417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="10" spans="1:8" ht="26" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -4444,7 +4443,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="11" spans="1:8" ht="26" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -4470,7 +4469,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="12" spans="1:8" ht="26" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -4496,7 +4495,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="13" spans="1:8" ht="26" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -4522,7 +4521,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="14" spans="1:8" ht="26" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
@@ -4548,7 +4547,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="15" spans="1:8" ht="26" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
@@ -4574,7 +4573,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="57" hidden="1" customHeight="1">
+    <row r="16" spans="1:8" ht="57" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>1</v>
       </c>
@@ -4600,7 +4599,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="39" hidden="1" customHeight="1">
+    <row r="17" spans="1:8" ht="39" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
@@ -4626,7 +4625,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="18" spans="1:8" ht="26" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
@@ -4652,7 +4651,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="19" spans="1:8" ht="26" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>1</v>
       </c>
@@ -4678,7 +4677,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="20" spans="1:8" ht="26" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
@@ -4704,7 +4703,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="21" spans="1:8" ht="26" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
@@ -4730,7 +4729,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="22" spans="1:8" ht="26" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>1</v>
       </c>
@@ -4756,7 +4755,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="23" spans="1:8" ht="26" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
@@ -4782,7 +4781,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="24" spans="1:8" ht="26" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>1</v>
       </c>
@@ -4808,7 +4807,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="25" spans="1:8" ht="26" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>1</v>
       </c>
@@ -4834,7 +4833,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="26" spans="1:8" ht="26" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>1</v>
       </c>
@@ -4860,7 +4859,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="26" hidden="1" customHeight="1">
+    <row r="27" spans="1:8" ht="26" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
@@ -4886,7 +4885,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="29" hidden="1" customHeight="1">
+    <row r="28" spans="1:8" ht="29" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
@@ -4912,7 +4911,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="17" hidden="1">
+    <row r="29" spans="1:8" ht="17">
       <c r="A29" s="1" t="s">
         <v>1</v>
       </c>
@@ -4938,7 +4937,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="33" hidden="1" customHeight="1">
+    <row r="30" spans="1:8" ht="33" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
@@ -4964,7 +4963,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="31" spans="1:8" ht="24" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
@@ -4990,7 +4989,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="32" spans="1:8" ht="24" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
@@ -5016,7 +5015,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="33" spans="1:8" ht="24" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
@@ -5042,7 +5041,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="34" spans="1:8" ht="24" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
@@ -5068,7 +5067,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="35" spans="1:8" ht="24" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
@@ -5094,7 +5093,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="36" spans="1:8" ht="24" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>1</v>
       </c>
@@ -5120,7 +5119,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="37" spans="1:8" ht="24" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>1</v>
       </c>
@@ -5146,7 +5145,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="38" spans="1:8" ht="24" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>1</v>
       </c>
@@ -5172,7 +5171,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="39" spans="1:8" ht="24" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>1</v>
       </c>
@@ -5198,7 +5197,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="40" spans="1:8" ht="24" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>1</v>
       </c>
@@ -5224,7 +5223,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="29" hidden="1" customHeight="1">
+    <row r="41" spans="1:8" ht="29" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>93</v>
       </c>
@@ -5250,7 +5249,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="42" spans="1:8" ht="24" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>93</v>
       </c>
@@ -5276,7 +5275,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="43" spans="1:8" ht="24" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>93</v>
       </c>
@@ -5302,7 +5301,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="44" spans="1:8" ht="24" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>93</v>
       </c>
@@ -5328,7 +5327,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="45" spans="1:8" ht="24" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>93</v>
       </c>
@@ -5354,7 +5353,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="46" spans="1:8" ht="24" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>93</v>
       </c>
@@ -5380,7 +5379,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="47" spans="1:8" ht="24" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
@@ -5406,7 +5405,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="48" spans="1:8" ht="24" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>93</v>
       </c>
@@ -5432,7 +5431,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="49" spans="1:8" ht="24" customHeight="1">
       <c r="A49" s="1" t="s">
         <v>93</v>
       </c>
@@ -5458,7 +5457,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="50" spans="1:8" ht="24" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>93</v>
       </c>
@@ -5484,7 +5483,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="51" spans="1:8" ht="24" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>93</v>
       </c>
@@ -5510,7 +5509,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="52" spans="1:8" ht="24" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>93</v>
       </c>
@@ -5536,7 +5535,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="53" spans="1:8" ht="24" customHeight="1">
       <c r="A53" s="1" t="s">
         <v>93</v>
       </c>
@@ -5562,7 +5561,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="54" spans="1:8" ht="24" customHeight="1">
       <c r="A54" s="1" t="s">
         <v>93</v>
       </c>
@@ -5588,7 +5587,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="55" spans="1:8" ht="24" customHeight="1">
       <c r="A55" s="1" t="s">
         <v>93</v>
       </c>
@@ -5614,7 +5613,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="56" spans="1:8" ht="24" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>93</v>
       </c>
@@ -5640,7 +5639,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="57" spans="1:8" ht="24" customHeight="1">
       <c r="A57" s="1" t="s">
         <v>93</v>
       </c>
@@ -5666,7 +5665,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="58" spans="1:8" ht="24" customHeight="1">
       <c r="A58" s="1" t="s">
         <v>93</v>
       </c>
@@ -5692,7 +5691,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="59" spans="1:8" ht="24" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>93</v>
       </c>
@@ -5718,7 +5717,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="60" spans="1:8" ht="24" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>93</v>
       </c>
@@ -5744,7 +5743,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="61" spans="1:8" ht="24" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>93</v>
       </c>
@@ -5770,7 +5769,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="62" spans="1:8" ht="24" customHeight="1">
       <c r="A62" s="1" t="s">
         <v>93</v>
       </c>
@@ -5796,7 +5795,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="63" spans="1:8" ht="24" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>93</v>
       </c>
@@ -5822,7 +5821,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="64" spans="1:8" ht="24" customHeight="1">
       <c r="A64" s="1" t="s">
         <v>93</v>
       </c>
@@ -5848,7 +5847,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="65" spans="1:8" ht="24" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>93</v>
       </c>
@@ -5874,7 +5873,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="35" hidden="1" customHeight="1">
+    <row r="66" spans="1:8" ht="35" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>93</v>
       </c>
@@ -5900,7 +5899,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="67" spans="1:8" ht="24" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>93</v>
       </c>
@@ -5926,7 +5925,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="68" spans="1:8" ht="24" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>93</v>
       </c>
@@ -5952,7 +5951,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="69" spans="1:8" ht="24" customHeight="1">
       <c r="A69" s="1" t="s">
         <v>93</v>
       </c>
@@ -5978,7 +5977,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="70" spans="1:8" ht="24" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>93</v>
       </c>
@@ -6004,7 +6003,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="71" spans="1:8" ht="24" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>93</v>
       </c>
@@ -6030,7 +6029,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="72" spans="1:8" ht="24" customHeight="1">
       <c r="A72" s="1" t="s">
         <v>93</v>
       </c>
@@ -6056,7 +6055,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="73" spans="1:8" ht="24" customHeight="1">
       <c r="A73" s="1" t="s">
         <v>93</v>
       </c>
@@ -6082,7 +6081,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="74" spans="1:8" ht="24" customHeight="1">
       <c r="A74" s="1" t="s">
         <v>93</v>
       </c>
@@ -6108,7 +6107,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="35" hidden="1" customHeight="1">
+    <row r="75" spans="1:8" ht="35" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>93</v>
       </c>
@@ -6134,7 +6133,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="76" spans="1:8" ht="24" customHeight="1">
       <c r="A76" s="1" t="s">
         <v>93</v>
       </c>
@@ -6160,7 +6159,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="77" spans="1:8" ht="24" customHeight="1">
       <c r="A77" s="1" t="s">
         <v>93</v>
       </c>
@@ -6186,7 +6185,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="78" spans="1:8" ht="24" customHeight="1">
       <c r="A78" s="1" t="s">
         <v>93</v>
       </c>
@@ -6212,7 +6211,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="79" spans="1:8" ht="24" customHeight="1">
       <c r="A79" s="1" t="s">
         <v>93</v>
       </c>
@@ -6238,7 +6237,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="80" spans="1:8" ht="24" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>93</v>
       </c>
@@ -6264,7 +6263,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="81" spans="1:8" ht="24" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>93</v>
       </c>
@@ -6290,7 +6289,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="82" spans="1:8" ht="24" customHeight="1">
       <c r="A82" s="1" t="s">
         <v>93</v>
       </c>
@@ -6316,7 +6315,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="83" spans="1:8" ht="24" customHeight="1">
       <c r="A83" s="1" t="s">
         <v>93</v>
       </c>
@@ -6342,7 +6341,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="84" spans="1:8" ht="24" customHeight="1">
       <c r="A84" s="1" t="s">
         <v>93</v>
       </c>
@@ -6368,7 +6367,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="85" spans="1:8" ht="24" customHeight="1">
       <c r="A85" s="1" t="s">
         <v>93</v>
       </c>
@@ -6394,7 +6393,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="86" spans="1:8" ht="24" customHeight="1">
       <c r="A86" s="1" t="s">
         <v>93</v>
       </c>
@@ -6420,7 +6419,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="87" spans="1:8" ht="24" customHeight="1">
       <c r="A87" s="1" t="s">
         <v>93</v>
       </c>
@@ -6446,7 +6445,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="88" spans="1:8" ht="24" customHeight="1">
       <c r="A88" s="1" t="s">
         <v>93</v>
       </c>
@@ -6472,7 +6471,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="89" spans="1:8" ht="24" customHeight="1">
       <c r="A89" s="1" t="s">
         <v>93</v>
       </c>
@@ -6498,7 +6497,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="90" spans="1:8" ht="24" customHeight="1">
       <c r="A90" s="1" t="s">
         <v>93</v>
       </c>
@@ -6524,7 +6523,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="91" spans="1:8" ht="24" customHeight="1">
       <c r="A91" s="1" t="s">
         <v>93</v>
       </c>
@@ -6550,7 +6549,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="92" spans="1:8" ht="24" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>93</v>
       </c>
@@ -6576,7 +6575,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="93" spans="1:8" ht="24" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>93</v>
       </c>
@@ -6602,7 +6601,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="94" spans="1:8" ht="24" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>93</v>
       </c>
@@ -6628,7 +6627,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="95" spans="1:8" ht="24" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
@@ -6654,7 +6653,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="96" spans="1:8" ht="24" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>93</v>
       </c>
@@ -6680,7 +6679,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="97" spans="1:8" ht="24" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>93</v>
       </c>
@@ -6706,7 +6705,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="98" spans="1:8" ht="24" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>93</v>
       </c>
@@ -6732,7 +6731,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="99" spans="1:8" ht="24" customHeight="1">
       <c r="A99" s="1" t="s">
         <v>93</v>
       </c>
@@ -6758,7 +6757,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="100" spans="1:8" ht="24" customHeight="1">
       <c r="A100" s="1" t="s">
         <v>93</v>
       </c>
@@ -6784,7 +6783,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="101" spans="1:8" ht="24" customHeight="1">
       <c r="A101" s="1" t="s">
         <v>222</v>
       </c>
@@ -6810,7 +6809,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="102" spans="1:8" ht="24" customHeight="1">
       <c r="A102" s="1" t="s">
         <v>222</v>
       </c>
@@ -6836,7 +6835,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="103" spans="1:8" ht="24" customHeight="1">
       <c r="A103" s="1" t="s">
         <v>222</v>
       </c>
@@ -6862,7 +6861,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="104" spans="1:8" ht="24" customHeight="1">
       <c r="A104" s="1" t="s">
         <v>222</v>
       </c>
@@ -6888,7 +6887,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="105" spans="1:8" ht="24" customHeight="1">
       <c r="A105" s="1" t="s">
         <v>222</v>
       </c>
@@ -6914,7 +6913,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="106" spans="1:8" ht="24" customHeight="1">
       <c r="A106" s="1" t="s">
         <v>222</v>
       </c>
@@ -6940,7 +6939,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="107" spans="1:8" ht="24" customHeight="1">
       <c r="A107" s="1" t="s">
         <v>222</v>
       </c>
@@ -6966,7 +6965,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="108" spans="1:8" ht="24" customHeight="1">
       <c r="A108" s="1" t="s">
         <v>222</v>
       </c>
@@ -6992,7 +6991,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="109" spans="1:8" ht="24" customHeight="1">
       <c r="A109" s="1" t="s">
         <v>222</v>
       </c>
@@ -7018,7 +7017,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="110" spans="1:8" ht="24" customHeight="1">
       <c r="A110" s="1" t="s">
         <v>222</v>
       </c>
@@ -7044,7 +7043,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="111" spans="1:8" ht="24" customHeight="1">
       <c r="A111" s="1" t="s">
         <v>222</v>
       </c>
@@ -7070,7 +7069,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="112" spans="1:8" ht="24" customHeight="1">
       <c r="A112" s="1" t="s">
         <v>222</v>
       </c>
@@ -7096,7 +7095,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="113" spans="1:8" ht="24" customHeight="1">
       <c r="A113" s="1" t="s">
         <v>222</v>
       </c>
@@ -7122,7 +7121,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="114" spans="1:8" ht="24" customHeight="1">
       <c r="A114" s="1" t="s">
         <v>222</v>
       </c>
@@ -7148,7 +7147,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="115" spans="1:8" ht="24" customHeight="1">
       <c r="A115" s="1" t="s">
         <v>222</v>
       </c>
@@ -7174,7 +7173,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="116" spans="1:8" ht="24" customHeight="1">
       <c r="A116" s="1" t="s">
         <v>222</v>
       </c>
@@ -7200,7 +7199,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="117" spans="1:8" ht="24" customHeight="1">
       <c r="A117" s="1" t="s">
         <v>222</v>
       </c>
@@ -7226,7 +7225,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="118" spans="1:8" ht="24" customHeight="1">
       <c r="A118" s="1" t="s">
         <v>222</v>
       </c>
@@ -7252,7 +7251,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="119" spans="1:8" ht="24" customHeight="1">
       <c r="A119" s="1" t="s">
         <v>222</v>
       </c>
@@ -7278,7 +7277,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="120" spans="1:8" ht="24" customHeight="1">
       <c r="A120" s="1" t="s">
         <v>222</v>
       </c>
@@ -7304,7 +7303,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="121" spans="1:8" ht="24" customHeight="1">
       <c r="A121" s="1" t="s">
         <v>222</v>
       </c>
@@ -7330,7 +7329,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="122" spans="1:8" ht="24" customHeight="1">
       <c r="A122" s="1" t="s">
         <v>222</v>
       </c>
@@ -7356,7 +7355,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="123" spans="1:8" ht="24" customHeight="1">
       <c r="A123" s="1" t="s">
         <v>222</v>
       </c>
@@ -7382,7 +7381,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="124" spans="1:8" ht="24" customHeight="1">
       <c r="A124" s="1" t="s">
         <v>222</v>
       </c>
@@ -7408,7 +7407,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="125" spans="1:8" ht="24" customHeight="1">
       <c r="A125" s="1" t="s">
         <v>222</v>
       </c>
@@ -7434,7 +7433,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="126" spans="1:8" ht="24" customHeight="1">
       <c r="A126" s="1" t="s">
         <v>222</v>
       </c>
@@ -7460,7 +7459,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="127" spans="1:8" ht="24" customHeight="1">
       <c r="A127" s="1" t="s">
         <v>222</v>
       </c>
@@ -7486,7 +7485,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="128" spans="1:8" ht="24" customHeight="1">
       <c r="A128" s="1" t="s">
         <v>222</v>
       </c>
@@ -7512,7 +7511,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="129" spans="1:8" ht="24" customHeight="1">
       <c r="A129" s="1" t="s">
         <v>222</v>
       </c>
@@ -7538,7 +7537,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="130" spans="1:8" ht="24" customHeight="1">
       <c r="A130" s="1" t="s">
         <v>222</v>
       </c>
@@ -7564,7 +7563,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="131" spans="1:8" ht="24" customHeight="1">
       <c r="A131" s="1" t="s">
         <v>222</v>
       </c>
@@ -7590,7 +7589,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="132" spans="1:8" ht="24" customHeight="1">
       <c r="A132" s="1" t="s">
         <v>222</v>
       </c>
@@ -7616,7 +7615,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="133" spans="1:8" ht="24" customHeight="1">
       <c r="A133" s="1" t="s">
         <v>222</v>
       </c>
@@ -7642,7 +7641,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="134" spans="1:8" ht="24" customHeight="1">
       <c r="A134" s="1" t="s">
         <v>222</v>
       </c>
@@ -7668,7 +7667,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="135" spans="1:8" ht="24" customHeight="1">
       <c r="A135" s="1" t="s">
         <v>222</v>
       </c>
@@ -7694,7 +7693,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="136" spans="1:8" ht="24" customHeight="1">
       <c r="A136" s="1" t="s">
         <v>222</v>
       </c>
@@ -7720,7 +7719,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="137" spans="1:8" ht="24" customHeight="1">
       <c r="A137" s="1" t="s">
         <v>222</v>
       </c>
@@ -7746,7 +7745,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="138" spans="1:8" ht="24" customHeight="1">
       <c r="A138" s="1" t="s">
         <v>222</v>
       </c>
@@ -7772,7 +7771,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="139" spans="1:8" ht="24" customHeight="1">
       <c r="A139" s="1" t="s">
         <v>222</v>
       </c>
@@ -7798,7 +7797,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="140" spans="1:8" ht="24" customHeight="1">
       <c r="A140" s="1" t="s">
         <v>222</v>
       </c>
@@ -7824,7 +7823,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="141" spans="1:8" ht="24" customHeight="1">
       <c r="A141" s="1" t="s">
         <v>222</v>
       </c>
@@ -7850,7 +7849,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="142" spans="1:8" ht="24" customHeight="1">
       <c r="A142" s="1" t="s">
         <v>222</v>
       </c>
@@ -7876,7 +7875,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="143" spans="1:8" ht="24" customHeight="1">
       <c r="A143" s="1" t="s">
         <v>222</v>
       </c>
@@ -7902,7 +7901,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="144" spans="1:8" ht="24" customHeight="1">
       <c r="A144" s="1" t="s">
         <v>222</v>
       </c>
@@ -7928,7 +7927,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="145" spans="1:8" ht="24" customHeight="1">
       <c r="A145" s="1" t="s">
         <v>222</v>
       </c>
@@ -7954,7 +7953,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="146" spans="1:8" ht="24" customHeight="1">
       <c r="A146" s="1" t="s">
         <v>222</v>
       </c>
@@ -7980,7 +7979,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="147" spans="1:8" ht="24" customHeight="1">
       <c r="A147" s="1" t="s">
         <v>222</v>
       </c>
@@ -8006,7 +8005,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="148" spans="1:8" ht="24" customHeight="1">
       <c r="A148" s="1" t="s">
         <v>222</v>
       </c>
@@ -8032,7 +8031,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="149" spans="1:8" ht="24" customHeight="1">
       <c r="A149" s="1" t="s">
         <v>222</v>
       </c>
@@ -8058,7 +8057,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="150" spans="1:8" ht="24" customHeight="1">
       <c r="A150" s="1" t="s">
         <v>222</v>
       </c>
@@ -8084,7 +8083,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="151" spans="1:8" ht="24" customHeight="1">
       <c r="A151" s="1" t="s">
         <v>222</v>
       </c>
@@ -8110,7 +8109,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="152" spans="1:8" ht="24" customHeight="1">
       <c r="A152" s="1" t="s">
         <v>222</v>
       </c>
@@ -8136,7 +8135,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="153" spans="1:8" ht="24" customHeight="1">
       <c r="A153" s="1" t="s">
         <v>222</v>
       </c>
@@ -8162,7 +8161,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="154" spans="1:8" ht="24" customHeight="1">
       <c r="A154" s="1" t="s">
         <v>222</v>
       </c>
@@ -8188,7 +8187,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="155" spans="1:8" ht="24" customHeight="1">
       <c r="A155" s="1" t="s">
         <v>222</v>
       </c>
@@ -8214,7 +8213,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="156" spans="1:8" ht="24" customHeight="1">
       <c r="A156" s="1" t="s">
         <v>222</v>
       </c>
@@ -8240,7 +8239,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="157" spans="1:8" ht="24" customHeight="1">
       <c r="A157" s="1" t="s">
         <v>222</v>
       </c>
@@ -8266,7 +8265,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="158" spans="1:8" ht="24" customHeight="1">
       <c r="A158" s="1" t="s">
         <v>222</v>
       </c>
@@ -8292,7 +8291,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="159" spans="1:8" ht="24" customHeight="1">
       <c r="A159" s="1" t="s">
         <v>222</v>
       </c>
@@ -8318,7 +8317,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="160" spans="1:8" ht="24" customHeight="1">
       <c r="A160" s="1" t="s">
         <v>222</v>
       </c>
@@ -8344,7 +8343,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="161" spans="1:8" ht="24" customHeight="1">
       <c r="A161" s="1" t="s">
         <v>222</v>
       </c>
@@ -8370,7 +8369,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="162" spans="1:8" ht="24" customHeight="1">
       <c r="A162" s="1" t="s">
         <v>222</v>
       </c>
@@ -8396,7 +8395,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="163" spans="1:8" ht="24" customHeight="1">
       <c r="A163" s="1" t="s">
         <v>222</v>
       </c>
@@ -8422,7 +8421,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="164" spans="1:8" ht="24" customHeight="1">
       <c r="A164" s="1" t="s">
         <v>222</v>
       </c>
@@ -8448,7 +8447,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="165" spans="1:8" ht="24" customHeight="1">
       <c r="A165" s="1" t="s">
         <v>222</v>
       </c>
@@ -8474,7 +8473,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="166" spans="1:8" ht="24" customHeight="1">
       <c r="A166" s="1" t="s">
         <v>222</v>
       </c>
@@ -8500,7 +8499,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="167" spans="1:8" ht="24" customHeight="1">
       <c r="A167" s="1" t="s">
         <v>222</v>
       </c>
@@ -8526,7 +8525,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="168" spans="1:8" ht="24" customHeight="1">
       <c r="A168" s="1" t="s">
         <v>222</v>
       </c>
@@ -8552,7 +8551,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="169" spans="1:8" ht="24" customHeight="1">
       <c r="A169" s="1" t="s">
         <v>222</v>
       </c>
@@ -8578,7 +8577,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="170" spans="1:8" ht="24" customHeight="1">
       <c r="A170" s="1" t="s">
         <v>222</v>
       </c>
@@ -8604,7 +8603,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="171" spans="1:8" ht="24" customHeight="1">
       <c r="A171" s="1" t="s">
         <v>222</v>
       </c>
@@ -10424,7 +10423,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="241" spans="1:8" ht="24" customHeight="1">
       <c r="A241" s="1" t="s">
         <v>515</v>
       </c>
@@ -10450,7 +10449,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="242" spans="1:8" ht="24" customHeight="1">
       <c r="A242" s="1" t="s">
         <v>515</v>
       </c>
@@ -10476,7 +10475,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="243" spans="1:8" ht="24" customHeight="1">
       <c r="A243" s="1" t="s">
         <v>515</v>
       </c>
@@ -10502,7 +10501,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="244" spans="1:8" ht="24" customHeight="1">
       <c r="A244" s="1" t="s">
         <v>515</v>
       </c>
@@ -10528,7 +10527,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="245" spans="1:8" ht="24" customHeight="1">
       <c r="A245" s="1" t="s">
         <v>515</v>
       </c>
@@ -10554,7 +10553,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="246" spans="1:8" ht="24" customHeight="1">
       <c r="A246" s="1" t="s">
         <v>515</v>
       </c>
@@ -10580,7 +10579,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="247" spans="1:8" ht="24" customHeight="1">
       <c r="A247" s="1" t="s">
         <v>515</v>
       </c>
@@ -10606,7 +10605,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="248" spans="1:8" ht="24" customHeight="1">
       <c r="A248" s="1" t="s">
         <v>515</v>
       </c>
@@ -10632,7 +10631,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="249" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="249" spans="1:8" ht="24" customHeight="1">
       <c r="A249" s="1" t="s">
         <v>515</v>
       </c>
@@ -10658,7 +10657,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="250" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="250" spans="1:8" ht="24" customHeight="1">
       <c r="A250" s="1" t="s">
         <v>515</v>
       </c>
@@ -10684,7 +10683,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="251" spans="1:8" ht="24" customHeight="1">
       <c r="A251" s="1" t="s">
         <v>515</v>
       </c>
@@ -10710,7 +10709,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="252" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="252" spans="1:8" ht="24" customHeight="1">
       <c r="A252" s="1" t="s">
         <v>515</v>
       </c>
@@ -10736,7 +10735,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="253" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="253" spans="1:8" ht="24" customHeight="1">
       <c r="A253" s="1" t="s">
         <v>515</v>
       </c>
@@ -10762,7 +10761,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="254" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="254" spans="1:8" ht="24" customHeight="1">
       <c r="A254" s="1" t="s">
         <v>515</v>
       </c>
@@ -10788,7 +10787,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="255" spans="1:8" ht="24" customHeight="1">
       <c r="A255" s="1" t="s">
         <v>515</v>
       </c>
@@ -10814,7 +10813,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="256" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="256" spans="1:8" ht="24" customHeight="1">
       <c r="A256" s="1" t="s">
         <v>515</v>
       </c>
@@ -10840,7 +10839,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="257" spans="1:8" ht="24" customHeight="1">
       <c r="A257" s="1" t="s">
         <v>515</v>
       </c>
@@ -10866,7 +10865,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="258" spans="1:8" ht="24" customHeight="1">
       <c r="A258" s="1" t="s">
         <v>515</v>
       </c>
@@ -10892,7 +10891,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="259" spans="1:8" ht="24" customHeight="1">
       <c r="A259" s="1" t="s">
         <v>515</v>
       </c>
@@ -10918,7 +10917,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="260" spans="1:8" ht="24" customHeight="1">
       <c r="A260" s="1" t="s">
         <v>515</v>
       </c>
@@ -10944,7 +10943,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="261" spans="1:8" ht="24" customHeight="1">
       <c r="A261" s="1" t="s">
         <v>515</v>
       </c>
@@ -10970,7 +10969,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="262" spans="1:8" ht="24" customHeight="1">
       <c r="A262" s="1" t="s">
         <v>515</v>
       </c>
@@ -10996,7 +10995,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="263" spans="1:8" ht="24" customHeight="1">
       <c r="A263" s="1" t="s">
         <v>515</v>
       </c>
@@ -11022,7 +11021,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="264" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="264" spans="1:8" ht="24" customHeight="1">
       <c r="A264" s="1" t="s">
         <v>515</v>
       </c>
@@ -11048,7 +11047,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="265" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="265" spans="1:8" ht="24" customHeight="1">
       <c r="A265" s="1" t="s">
         <v>515</v>
       </c>
@@ -11074,7 +11073,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="266" spans="1:8" ht="24" customHeight="1">
       <c r="A266" s="1" t="s">
         <v>515</v>
       </c>
@@ -11100,7 +11099,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="267" spans="1:8" ht="24" customHeight="1">
       <c r="A267" s="1" t="s">
         <v>515</v>
       </c>
@@ -11126,7 +11125,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="268" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="268" spans="1:8" ht="24" customHeight="1">
       <c r="A268" s="1" t="s">
         <v>515</v>
       </c>
@@ -11152,7 +11151,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="269" spans="1:8" ht="24" customHeight="1">
       <c r="A269" s="1" t="s">
         <v>515</v>
       </c>
@@ -11178,7 +11177,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="270" spans="1:8" ht="24" customHeight="1">
       <c r="A270" s="1" t="s">
         <v>515</v>
       </c>
@@ -11204,7 +11203,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="271" spans="1:8" ht="24" customHeight="1">
       <c r="A271" s="1" t="s">
         <v>515</v>
       </c>
@@ -11230,7 +11229,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="272" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="272" spans="1:8" ht="24" customHeight="1">
       <c r="A272" s="1" t="s">
         <v>515</v>
       </c>
@@ -11256,7 +11255,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="273" spans="1:8" ht="24" customHeight="1">
       <c r="A273" s="1" t="s">
         <v>515</v>
       </c>
@@ -11282,7 +11281,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="274" spans="1:8" ht="24" customHeight="1">
       <c r="A274" s="1" t="s">
         <v>515</v>
       </c>
@@ -11308,7 +11307,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="275" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="275" spans="1:8" ht="24" customHeight="1">
       <c r="A275" s="1" t="s">
         <v>515</v>
       </c>
@@ -11334,7 +11333,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="276" spans="1:8" ht="24" customHeight="1">
       <c r="A276" s="1" t="s">
         <v>515</v>
       </c>
@@ -11360,7 +11359,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="277" spans="1:8" ht="24" customHeight="1">
       <c r="A277" s="1" t="s">
         <v>515</v>
       </c>
@@ -11386,7 +11385,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="278" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="278" spans="1:8" ht="24" customHeight="1">
       <c r="A278" s="1" t="s">
         <v>515</v>
       </c>
@@ -11412,7 +11411,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="279" spans="1:8" ht="24" customHeight="1">
       <c r="A279" s="1" t="s">
         <v>515</v>
       </c>
@@ -11438,7 +11437,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="280" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="280" spans="1:8" ht="24" customHeight="1">
       <c r="A280" s="1" t="s">
         <v>515</v>
       </c>
@@ -11464,7 +11463,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="281" spans="1:8" ht="24" customHeight="1">
       <c r="A281" s="1" t="s">
         <v>515</v>
       </c>
@@ -11490,7 +11489,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="282" spans="1:8" ht="24" customHeight="1">
       <c r="A282" s="1" t="s">
         <v>515</v>
       </c>
@@ -11516,7 +11515,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="283" spans="1:8" ht="24" customHeight="1">
       <c r="A283" s="1" t="s">
         <v>515</v>
       </c>
@@ -11542,7 +11541,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="284" spans="1:8" ht="24" customHeight="1">
       <c r="A284" s="1" t="s">
         <v>515</v>
       </c>
@@ -11568,7 +11567,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="285" spans="1:8" ht="24" customHeight="1">
       <c r="A285" s="1" t="s">
         <v>515</v>
       </c>
@@ -11594,7 +11593,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="286" spans="1:8" ht="24" customHeight="1">
       <c r="A286" s="1" t="s">
         <v>515</v>
       </c>
@@ -11620,7 +11619,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="287" spans="1:8" ht="24" customHeight="1">
       <c r="A287" s="1" t="s">
         <v>515</v>
       </c>
@@ -11646,7 +11645,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="288" spans="1:8" ht="24" customHeight="1">
       <c r="A288" s="1" t="s">
         <v>515</v>
       </c>
@@ -11672,7 +11671,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="289" spans="1:8" ht="24" customHeight="1">
       <c r="A289" s="1" t="s">
         <v>515</v>
       </c>
@@ -11698,7 +11697,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="290" spans="1:8" ht="24" customHeight="1">
       <c r="A290" s="1" t="s">
         <v>515</v>
       </c>
@@ -11724,7 +11723,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="291" spans="1:8" ht="24" customHeight="1">
       <c r="A291" s="1" t="s">
         <v>515</v>
       </c>
@@ -11750,7 +11749,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="292" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="292" spans="1:8" ht="24" customHeight="1">
       <c r="A292" s="1" t="s">
         <v>515</v>
       </c>
@@ -11776,7 +11775,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="293" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="293" spans="1:8" ht="24" customHeight="1">
       <c r="A293" s="1" t="s">
         <v>515</v>
       </c>
@@ -11802,7 +11801,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="294" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="294" spans="1:8" ht="24" customHeight="1">
       <c r="A294" s="1" t="s">
         <v>515</v>
       </c>
@@ -11828,7 +11827,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="295" spans="1:8" ht="24" customHeight="1">
       <c r="A295" s="1" t="s">
         <v>515</v>
       </c>
@@ -11854,7 +11853,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="296" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="296" spans="1:8" ht="24" customHeight="1">
       <c r="A296" s="1" t="s">
         <v>515</v>
       </c>
@@ -11880,7 +11879,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="297" spans="1:8" ht="24" customHeight="1">
       <c r="A297" s="1" t="s">
         <v>515</v>
       </c>
@@ -11906,7 +11905,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="298" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="298" spans="1:8" ht="24" customHeight="1">
       <c r="A298" s="1" t="s">
         <v>515</v>
       </c>
@@ -11932,7 +11931,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="299" spans="1:8" ht="24" customHeight="1">
       <c r="A299" s="1" t="s">
         <v>515</v>
       </c>
@@ -11958,7 +11957,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="300" spans="1:8" ht="24" customHeight="1">
       <c r="A300" s="1" t="s">
         <v>515</v>
       </c>
@@ -11984,7 +11983,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="301" spans="1:8" ht="24" customHeight="1">
       <c r="A301" s="1" t="s">
         <v>515</v>
       </c>
@@ -12010,7 +12009,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="302" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="302" spans="1:8" ht="24" customHeight="1">
       <c r="A302" s="1" t="s">
         <v>515</v>
       </c>
@@ -12036,7 +12035,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="303" spans="1:8" ht="24" customHeight="1">
       <c r="A303" s="1" t="s">
         <v>515</v>
       </c>
@@ -12062,7 +12061,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="304" spans="1:8" ht="24" customHeight="1">
       <c r="A304" s="1" t="s">
         <v>515</v>
       </c>
@@ -12088,7 +12087,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="305" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="305" spans="1:8" ht="24" customHeight="1">
       <c r="A305" s="1" t="s">
         <v>515</v>
       </c>
@@ -12114,7 +12113,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="306" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="306" spans="1:8" ht="24" customHeight="1">
       <c r="A306" s="1" t="s">
         <v>515</v>
       </c>
@@ -12140,7 +12139,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="307" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="307" spans="1:8" ht="24" customHeight="1">
       <c r="A307" s="1" t="s">
         <v>515</v>
       </c>
@@ -12166,7 +12165,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="308" spans="1:8" ht="24" customHeight="1">
       <c r="A308" s="1" t="s">
         <v>515</v>
       </c>
@@ -12192,7 +12191,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="309" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="309" spans="1:8" ht="24" customHeight="1">
       <c r="A309" s="1" t="s">
         <v>515</v>
       </c>
@@ -12218,7 +12217,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="310" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="310" spans="1:8" ht="24" customHeight="1">
       <c r="A310" s="1" t="s">
         <v>515</v>
       </c>
@@ -12244,7 +12243,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="311" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="311" spans="1:8" ht="24" customHeight="1">
       <c r="A311" s="1" t="s">
         <v>515</v>
       </c>
@@ -12270,7 +12269,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="312" spans="1:8" ht="24" customHeight="1">
       <c r="A312" s="1" t="s">
         <v>515</v>
       </c>
@@ -12296,7 +12295,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="313" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="313" spans="1:8" ht="24" customHeight="1">
       <c r="A313" s="1" t="s">
         <v>515</v>
       </c>
@@ -12322,7 +12321,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="314" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="314" spans="1:8" ht="24" customHeight="1">
       <c r="A314" s="1" t="s">
         <v>515</v>
       </c>
@@ -12348,7 +12347,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="315" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="315" spans="1:8" ht="24" customHeight="1">
       <c r="A315" s="1" t="s">
         <v>515</v>
       </c>
@@ -12374,7 +12373,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="316" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="316" spans="1:8" ht="24" customHeight="1">
       <c r="A316" s="1" t="s">
         <v>515</v>
       </c>
@@ -12400,7 +12399,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="317" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="317" spans="1:8" ht="24" customHeight="1">
       <c r="A317" s="1" t="s">
         <v>515</v>
       </c>
@@ -12426,7 +12425,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="318" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="318" spans="1:8" ht="24" customHeight="1">
       <c r="A318" s="1" t="s">
         <v>515</v>
       </c>
@@ -12452,7 +12451,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="319" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="319" spans="1:8" ht="24" customHeight="1">
       <c r="A319" s="1" t="s">
         <v>515</v>
       </c>
@@ -12478,7 +12477,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="320" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="320" spans="1:8" ht="24" customHeight="1">
       <c r="A320" s="1" t="s">
         <v>515</v>
       </c>
@@ -12504,7 +12503,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="321" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="321" spans="1:8" ht="24" customHeight="1">
       <c r="A321" s="1" t="s">
         <v>686</v>
       </c>
@@ -12530,7 +12529,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="322" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="322" spans="1:8" ht="24" customHeight="1">
       <c r="A322" s="1" t="s">
         <v>686</v>
       </c>
@@ -12556,7 +12555,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="323" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="323" spans="1:8" ht="24" customHeight="1">
       <c r="A323" s="1" t="s">
         <v>686</v>
       </c>
@@ -12582,7 +12581,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="324" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="324" spans="1:8" ht="24" customHeight="1">
       <c r="A324" s="1" t="s">
         <v>686</v>
       </c>
@@ -12608,7 +12607,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="325" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="325" spans="1:8" ht="24" customHeight="1">
       <c r="A325" s="1" t="s">
         <v>686</v>
       </c>
@@ -12634,7 +12633,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="326" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="326" spans="1:8" ht="24" customHeight="1">
       <c r="A326" s="1" t="s">
         <v>686</v>
       </c>
@@ -12660,7 +12659,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="327" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="327" spans="1:8" ht="24" customHeight="1">
       <c r="A327" s="1" t="s">
         <v>686</v>
       </c>
@@ -12686,7 +12685,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="328" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="328" spans="1:8" ht="24" customHeight="1">
       <c r="A328" s="1" t="s">
         <v>686</v>
       </c>
@@ -12712,7 +12711,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="329" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="329" spans="1:8" ht="24" customHeight="1">
       <c r="A329" s="1" t="s">
         <v>686</v>
       </c>
@@ -12738,7 +12737,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="330" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="330" spans="1:8" ht="24" customHeight="1">
       <c r="A330" s="1" t="s">
         <v>686</v>
       </c>
@@ -12764,7 +12763,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="331" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="331" spans="1:8" ht="24" customHeight="1">
       <c r="A331" s="1" t="s">
         <v>686</v>
       </c>
@@ -12790,7 +12789,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="332" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="332" spans="1:8" ht="24" customHeight="1">
       <c r="A332" s="1" t="s">
         <v>686</v>
       </c>
@@ -12816,7 +12815,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="333" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="333" spans="1:8" ht="24" customHeight="1">
       <c r="A333" s="1" t="s">
         <v>686</v>
       </c>
@@ -12842,7 +12841,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="334" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="334" spans="1:8" ht="24" customHeight="1">
       <c r="A334" s="1" t="s">
         <v>686</v>
       </c>
@@ -12868,7 +12867,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="335" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="335" spans="1:8" ht="24" customHeight="1">
       <c r="A335" s="1" t="s">
         <v>686</v>
       </c>
@@ -12894,7 +12893,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="336" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="336" spans="1:8" ht="24" customHeight="1">
       <c r="A336" s="1" t="s">
         <v>686</v>
       </c>
@@ -12920,7 +12919,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="337" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="337" spans="1:8" ht="24" customHeight="1">
       <c r="A337" s="1" t="s">
         <v>686</v>
       </c>
@@ -12946,7 +12945,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="338" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="338" spans="1:8" ht="24" customHeight="1">
       <c r="A338" s="1" t="s">
         <v>686</v>
       </c>
@@ -12972,7 +12971,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="339" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="339" spans="1:8" ht="24" customHeight="1">
       <c r="A339" s="1" t="s">
         <v>686</v>
       </c>
@@ -12998,7 +12997,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="340" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="340" spans="1:8" ht="24" customHeight="1">
       <c r="A340" s="1" t="s">
         <v>686</v>
       </c>
@@ -13024,7 +13023,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="341" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="341" spans="1:8" ht="24" customHeight="1">
       <c r="A341" s="1" t="s">
         <v>686</v>
       </c>
@@ -13050,7 +13049,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="342" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="342" spans="1:8" ht="24" customHeight="1">
       <c r="A342" s="1" t="s">
         <v>686</v>
       </c>
@@ -13076,7 +13075,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="343" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="343" spans="1:8" ht="24" customHeight="1">
       <c r="A343" s="1" t="s">
         <v>686</v>
       </c>
@@ -13102,7 +13101,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="344" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="344" spans="1:8" ht="24" customHeight="1">
       <c r="A344" s="1" t="s">
         <v>686</v>
       </c>
@@ -13128,7 +13127,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="345" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="345" spans="1:8" ht="24" customHeight="1">
       <c r="A345" s="1" t="s">
         <v>686</v>
       </c>
@@ -13154,7 +13153,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="346" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="346" spans="1:8" ht="24" customHeight="1">
       <c r="A346" s="1" t="s">
         <v>686</v>
       </c>
@@ -13180,7 +13179,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="347" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="347" spans="1:8" ht="24" customHeight="1">
       <c r="A347" s="1" t="s">
         <v>686</v>
       </c>
@@ -13206,7 +13205,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="348" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="348" spans="1:8" ht="24" customHeight="1">
       <c r="A348" s="1" t="s">
         <v>686</v>
       </c>
@@ -13232,7 +13231,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="349" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="349" spans="1:8" ht="24" customHeight="1">
       <c r="A349" s="1" t="s">
         <v>686</v>
       </c>
@@ -13258,7 +13257,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="350" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="350" spans="1:8" ht="24" customHeight="1">
       <c r="A350" s="1" t="s">
         <v>686</v>
       </c>
@@ -13284,7 +13283,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="351" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="351" spans="1:8" ht="24" customHeight="1">
       <c r="A351" s="1" t="s">
         <v>686</v>
       </c>
@@ -13310,7 +13309,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="352" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="352" spans="1:8" ht="24" customHeight="1">
       <c r="A352" s="1" t="s">
         <v>686</v>
       </c>
@@ -13336,7 +13335,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="353" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="353" spans="1:8" ht="24" customHeight="1">
       <c r="A353" s="1" t="s">
         <v>686</v>
       </c>
@@ -13362,7 +13361,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="354" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="354" spans="1:8" ht="24" customHeight="1">
       <c r="A354" s="1" t="s">
         <v>686</v>
       </c>
@@ -13388,7 +13387,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="355" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="355" spans="1:8" ht="24" customHeight="1">
       <c r="A355" s="1" t="s">
         <v>686</v>
       </c>
@@ -13414,7 +13413,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="356" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="356" spans="1:8" ht="24" customHeight="1">
       <c r="A356" s="1" t="s">
         <v>686</v>
       </c>
@@ -13440,7 +13439,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="357" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="357" spans="1:8" ht="24" customHeight="1">
       <c r="A357" s="1" t="s">
         <v>686</v>
       </c>
@@ -13466,7 +13465,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="358" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="358" spans="1:8" ht="24" customHeight="1">
       <c r="A358" s="1" t="s">
         <v>686</v>
       </c>
@@ -13492,7 +13491,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="359" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="359" spans="1:8" ht="24" customHeight="1">
       <c r="A359" s="1" t="s">
         <v>686</v>
       </c>
@@ -13518,7 +13517,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="360" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="360" spans="1:8" ht="24" customHeight="1">
       <c r="A360" s="1" t="s">
         <v>686</v>
       </c>
@@ -13544,7 +13543,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="361" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="361" spans="1:8" ht="24" customHeight="1">
       <c r="A361" s="1" t="s">
         <v>686</v>
       </c>
@@ -13570,7 +13569,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="362" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="362" spans="1:8" ht="24" customHeight="1">
       <c r="A362" s="1" t="s">
         <v>686</v>
       </c>
@@ -13596,7 +13595,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="363" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="363" spans="1:8" ht="24" customHeight="1">
       <c r="A363" s="1" t="s">
         <v>686</v>
       </c>
@@ -13622,7 +13621,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="364" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="364" spans="1:8" ht="24" customHeight="1">
       <c r="A364" s="1" t="s">
         <v>686</v>
       </c>
@@ -13648,7 +13647,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="365" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="365" spans="1:8" ht="24" customHeight="1">
       <c r="A365" s="1" t="s">
         <v>686</v>
       </c>
@@ -13674,7 +13673,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="366" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="366" spans="1:8" ht="24" customHeight="1">
       <c r="A366" s="1" t="s">
         <v>686</v>
       </c>
@@ -13700,7 +13699,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="367" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="367" spans="1:8" ht="24" customHeight="1">
       <c r="A367" s="1" t="s">
         <v>686</v>
       </c>
@@ -13726,7 +13725,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="368" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="368" spans="1:8" ht="24" customHeight="1">
       <c r="A368" s="1" t="s">
         <v>686</v>
       </c>
@@ -13752,7 +13751,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="369" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="369" spans="1:8" ht="24" customHeight="1">
       <c r="A369" s="1" t="s">
         <v>686</v>
       </c>
@@ -13778,7 +13777,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="370" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="370" spans="1:8" ht="24" customHeight="1">
       <c r="A370" s="1" t="s">
         <v>686</v>
       </c>
@@ -13804,7 +13803,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="371" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="371" spans="1:8" ht="24" customHeight="1">
       <c r="A371" s="1" t="s">
         <v>686</v>
       </c>
@@ -13830,7 +13829,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="372" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="372" spans="1:8" ht="24" customHeight="1">
       <c r="A372" s="1" t="s">
         <v>686</v>
       </c>
@@ -13856,7 +13855,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="373" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="373" spans="1:8" ht="24" customHeight="1">
       <c r="A373" s="1" t="s">
         <v>686</v>
       </c>
@@ -13882,7 +13881,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="374" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="374" spans="1:8" ht="24" customHeight="1">
       <c r="A374" s="1" t="s">
         <v>686</v>
       </c>
@@ -13908,7 +13907,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="375" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="375" spans="1:8" ht="24" customHeight="1">
       <c r="A375" s="1" t="s">
         <v>686</v>
       </c>
@@ -13934,7 +13933,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="376" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="376" spans="1:8" ht="24" customHeight="1">
       <c r="A376" s="1" t="s">
         <v>686</v>
       </c>
@@ -14032,13 +14031,7 @@
     <row r="446" ht="24" customHeight="1"/>
     <row r="447" ht="24" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:H376" xr:uid="{A69C5E3E-8CEE-9D4D-88A8-B62C489FB538}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="g4"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H376" xr:uid="{A69C5E3E-8CEE-9D4D-88A8-B62C489FB538}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
